--- a/final_data_pipeline/output/311423longform.xlsx
+++ b/final_data_pipeline/output/311423longform.xlsx
@@ -4767,7 +4767,7 @@
         <v>56</v>
       </c>
       <c r="AA50">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB50">
         <v>8000</v>
@@ -4850,7 +4850,7 @@
         <v>56</v>
       </c>
       <c r="AA51">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB51">
         <v>8000</v>
@@ -4933,7 +4933,7 @@
         <v>56</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5016,7 +5016,7 @@
         <v>56</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -5099,7 +5099,7 @@
         <v>56</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB54">
         <v>8000</v>
@@ -5182,7 +5182,7 @@
         <v>56</v>
       </c>
       <c r="AA55">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB55">
         <v>8000</v>
@@ -5763,7 +5763,7 @@
         <v>56</v>
       </c>
       <c r="AA62">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB62">
         <v>8000</v>
@@ -5846,7 +5846,7 @@
         <v>56</v>
       </c>
       <c r="AA63">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB63">
         <v>8000</v>
@@ -5929,7 +5929,7 @@
         <v>56</v>
       </c>
       <c r="AA64">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB64">
         <v>8000</v>
@@ -6012,7 +6012,7 @@
         <v>56</v>
       </c>
       <c r="AA65">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB65">
         <v>8000</v>
@@ -6095,7 +6095,7 @@
         <v>56</v>
       </c>
       <c r="AA66">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB66">
         <v>8000</v>
@@ -6178,7 +6178,7 @@
         <v>56</v>
       </c>
       <c r="AA67">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB67">
         <v>8000</v>
